--- a/Configs/Excel/CfgLevelInfo.xlsx
+++ b/Configs/Excel/CfgLevelInfo.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -381,7 +381,7 @@
     <t>1;44;67</t>
   </si>
   <si>
-    <t>1026;982;1001</t>
+    <t>522;526;528</t>
   </si>
   <si>
     <t>第3关</t>
@@ -393,7 +393,7 @@
     <t>13;33;68</t>
   </si>
   <si>
-    <t>409;1031;1030</t>
+    <t>122;527;1624</t>
   </si>
   <si>
     <t>锁链</t>
@@ -408,7 +408,7 @@
     <t>21;28;59</t>
   </si>
   <si>
-    <t>501;515;1032</t>
+    <t>318;717;1619</t>
   </si>
   <si>
     <t>第5关</t>
@@ -420,7 +420,7 @@
     <t>4;26;64</t>
   </si>
   <si>
-    <t>492;1248;1247</t>
+    <t>315;713;1777</t>
   </si>
   <si>
     <t>第6关</t>
@@ -432,7 +432,7 @@
     <t>16;42;54</t>
   </si>
   <si>
-    <t>362;345;1057</t>
+    <t>230;547;1721</t>
   </si>
   <si>
     <t>第7关</t>
@@ -444,7 +444,7 @@
     <t>6;36;60</t>
   </si>
   <si>
-    <t>331;1005;1227</t>
+    <t>219;526;1755</t>
   </si>
   <si>
     <t>冰块</t>
@@ -459,7 +459,7 @@
     <t>2;43;56</t>
   </si>
   <si>
-    <t>492;403;987</t>
+    <t>138;564;1805</t>
   </si>
   <si>
     <t>第9关</t>
@@ -471,7 +471,7 @@
     <t>18;38;65</t>
   </si>
   <si>
-    <t>362;352;1037</t>
+    <t>287;549;1763</t>
   </si>
   <si>
     <t>第10关</t>
@@ -1312,7 +1312,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1323,6 +1323,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1471,12 +1477,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1488,13 +1494,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1780,6 +1786,17 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1787,17 +1804,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1916,16 +1922,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1934,124 +1937,130 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2061,9 +2070,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2091,34 +2097,40 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2180,6 +2192,32 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
+<woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <bookInfo cellCmpFml="0">
+    <open main="184" threadCnt="1"/>
+    <sheetInfos>
+      <sheetInfo cellCmpFml="0" sheetStid="1">
+        <open main="70" threadCnt="1"/>
+      </sheetInfo>
+      <sheetInfo cellCmpFml="0" sheetStid="2">
+        <open threadCnt="1"/>
+      </sheetInfo>
+      <sheetInfo cellCmpFml="0" sheetStid="3">
+        <open threadCnt="1"/>
+      </sheetInfo>
+    </sheetInfos>
+  </bookInfo>
+</woInfos>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2441,19 +2479,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T123"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
     <col min="2" max="2" width="9" style="15"/>
-    <col min="3" max="4" width="25.2477876106195" style="15" customWidth="1"/>
-    <col min="5" max="5" width="25.2477876106195" style="16" customWidth="1"/>
-    <col min="6" max="7" width="25.2477876106195" style="15" customWidth="1"/>
-    <col min="8" max="8" width="16.7522123893805" style="15" customWidth="1"/>
-    <col min="9" max="13" width="15.3716814159292" style="15" customWidth="1"/>
-    <col min="14" max="17" width="23.7522123893805" style="15" customWidth="1"/>
-    <col min="18" max="18" width="11.5044247787611" style="8" customWidth="1"/>
+    <col min="3" max="4" width="25.25" style="15" customWidth="1"/>
+    <col min="5" max="5" width="25.25" style="16" customWidth="1"/>
+    <col min="6" max="7" width="25.25" style="15" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="15" customWidth="1"/>
+    <col min="9" max="13" width="15.375" style="15" customWidth="1"/>
+    <col min="14" max="17" width="23.75" style="15" customWidth="1"/>
+    <col min="18" max="18" width="11.5083333333333" style="8" customWidth="1"/>
     <col min="19" max="19" width="11" style="8" customWidth="1"/>
-    <col min="20" max="20" width="10.2477876106195" style="8" customWidth="1"/>
+    <col min="20" max="20" width="10.25" style="8" customWidth="1"/>
     <col min="21" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
@@ -2470,7 +2508,7 @@
       <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
@@ -2485,33 +2523,33 @@
       <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
     </row>
     <row r="2" s="10" customFormat="1" spans="1:20">
       <c r="A2" s="17" t="s">
@@ -2541,33 +2579,33 @@
       <c r="I2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="N2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="P2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
     </row>
     <row r="3" s="10" customFormat="1" spans="1:20">
       <c r="A3" s="17" t="s">
@@ -2597,82 +2635,82 @@
       <c r="I3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="L3" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
     </row>
     <row r="4" s="12" customFormat="1" spans="1:20">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="27">
-        <v>0</v>
-      </c>
-      <c r="C4" s="27" t="s">
+      <c r="B4" s="21">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="27">
-        <v>0</v>
-      </c>
-      <c r="F4" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="27">
-        <v>0</v>
-      </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27">
-        <v>0</v>
-      </c>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O4" s="27">
+      <c r="D4" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0</v>
+      </c>
+      <c r="F4" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="21">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21">
+        <v>0</v>
+      </c>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O4" s="21">
         <v>101</v>
       </c>
-      <c r="P4" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="27">
-        <v>0</v>
-      </c>
-      <c r="T4" s="28"/>
+      <c r="P4" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>0</v>
+      </c>
+      <c r="T4" s="31"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="22" t="s">
         <v>42</v>
       </c>
       <c r="B5" s="16">
@@ -2704,13 +2742,13 @@
       <c r="L5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O5" s="27">
+      <c r="N5" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O5" s="21">
         <v>104</v>
       </c>
       <c r="P5" s="16" t="b">
@@ -2722,199 +2760,199 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" s="12" customFormat="1" spans="1:20">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="21">
         <v>2</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="27">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="s">
+      <c r="D6" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="21">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21">
+        <v>0</v>
+      </c>
+      <c r="L6" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O6" s="27">
+      <c r="N6" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O6" s="21">
         <v>106</v>
       </c>
-      <c r="P6" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="27">
+      <c r="P6" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="21">
         <v>0</v>
       </c>
       <c r="R6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="T6" s="28"/>
-    </row>
-    <row r="7" s="12" customFormat="1" spans="1:20">
-      <c r="A7" s="26" t="s">
+      <c r="T6" s="31"/>
+    </row>
+    <row r="7" s="12" customFormat="1" spans="1:18">
+      <c r="A7" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="21">
         <v>3</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="27">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="s">
+      <c r="D7" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21">
+        <v>0</v>
+      </c>
+      <c r="L7" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O7" s="27">
+      <c r="N7" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O7" s="21">
         <v>111</v>
       </c>
-      <c r="P7" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="27">
+      <c r="P7" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="21">
         <v>0</v>
       </c>
       <c r="R7" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" s="12" customFormat="1" spans="1:20">
-      <c r="A8" s="26" t="s">
+    <row r="8" s="12" customFormat="1" spans="1:17">
+      <c r="A8" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="21">
         <v>4</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="27">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="s">
+      <c r="D8" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21">
+        <v>0</v>
+      </c>
+      <c r="L8" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="27" t="s">
+      <c r="M8" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="21">
         <v>10001</v>
       </c>
       <c r="O8" s="15">
         <v>112</v>
       </c>
-      <c r="P8" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="12" customFormat="1" spans="1:20">
-      <c r="A9" s="26" t="s">
+      <c r="P8" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="12" customFormat="1" spans="1:18">
+      <c r="A9" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="21">
         <v>5</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="27">
+      <c r="D9" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21">
         <v>100</v>
       </c>
-      <c r="F9" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="s">
+      <c r="F9" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21">
+        <v>0</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O9" s="27"/>
+      <c r="N9" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O9" s="21"/>
       <c r="P9" s="16" t="b">
         <v>0</v>
       </c>
@@ -2925,144 +2963,144 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" s="12" customFormat="1" spans="1:20">
-      <c r="A10" s="26" t="s">
+    <row r="10" s="12" customFormat="1" spans="1:18">
+      <c r="A10" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="21">
         <v>6</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="27">
-        <v>0</v>
-      </c>
-      <c r="F10" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="27">
-        <v>0</v>
-      </c>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27">
-        <v>0</v>
-      </c>
-      <c r="L10" s="27" t="s">
+      <c r="D10" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21">
+        <v>0</v>
+      </c>
+      <c r="L10" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O10" s="27">
+      <c r="N10" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O10" s="21">
         <v>110</v>
       </c>
-      <c r="P10" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="27">
+      <c r="P10" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="21">
         <v>0</v>
       </c>
       <c r="R10" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" s="12" customFormat="1" spans="1:20">
-      <c r="A11" s="26" t="s">
+    <row r="11" s="12" customFormat="1" spans="1:17">
+      <c r="A11" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="21">
         <v>7</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="27">
-        <v>0</v>
-      </c>
-      <c r="F11" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="27">
-        <v>0</v>
-      </c>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27">
-        <v>0</v>
-      </c>
-      <c r="L11" s="27" t="s">
+      <c r="D11" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="21">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21">
+        <v>0</v>
+      </c>
+      <c r="L11" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="N11" s="27">
-        <v>10001</v>
-      </c>
-      <c r="P11" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="12" customFormat="1" spans="1:20">
-      <c r="A12" s="26" t="s">
+      <c r="N11" s="21">
+        <v>10001</v>
+      </c>
+      <c r="P11" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="12" customFormat="1" spans="1:18">
+      <c r="A12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="21">
         <v>8</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="27">
-        <v>0</v>
-      </c>
-      <c r="F12" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="27">
-        <v>0</v>
-      </c>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27">
-        <v>0</v>
-      </c>
-      <c r="L12" s="27" t="s">
+      <c r="D12" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="21">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21">
+        <v>0</v>
+      </c>
+      <c r="L12" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O12" s="27"/>
+      <c r="N12" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O12" s="21"/>
       <c r="P12" s="16" t="b">
         <v>0</v>
       </c>
@@ -3073,8 +3111,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="29" t="s">
+    <row r="13" spans="1:18">
+      <c r="A13" s="22" t="s">
         <v>76</v>
       </c>
       <c r="B13" s="16">
@@ -3107,9 +3145,9 @@
         <v>66</v>
       </c>
       <c r="M13" s="16">
-        <v>1036</v>
-      </c>
-      <c r="N13" s="27">
+        <v>2598</v>
+      </c>
+      <c r="N13" s="21">
         <v>10001</v>
       </c>
       <c r="O13" s="16"/>
@@ -3123,96 +3161,96 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" s="12" customFormat="1" spans="1:20">
-      <c r="A14" s="26" t="s">
+    <row r="14" s="12" customFormat="1" spans="1:18">
+      <c r="A14" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="21">
         <v>10</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="27">
+      <c r="D14" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21">
         <v>-50</v>
       </c>
-      <c r="F14" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="27">
-        <v>0</v>
-      </c>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27">
-        <v>0</v>
-      </c>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O14" s="27">
+      <c r="F14" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21">
+        <v>0</v>
+      </c>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O14" s="21">
         <v>113</v>
       </c>
-      <c r="P14" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="27">
+      <c r="P14" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="21">
         <v>0</v>
       </c>
       <c r="R14" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" s="12" customFormat="1" spans="1:20">
-      <c r="A15" s="26" t="s">
+    <row r="15" s="12" customFormat="1" spans="1:19">
+      <c r="A15" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="21">
         <v>11</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="27">
+      <c r="D15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="21">
         <v>130</v>
       </c>
-      <c r="F15" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="27">
-        <v>0</v>
-      </c>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27">
-        <v>0</v>
-      </c>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O15" s="27">
+      <c r="F15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="21">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21">
+        <v>0</v>
+      </c>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O15" s="21">
         <v>124</v>
       </c>
-      <c r="P15" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="27">
+      <c r="P15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="21">
         <v>0</v>
       </c>
       <c r="R15" s="13" t="s">
@@ -3222,8 +3260,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="29" t="s">
+    <row r="16" spans="1:19">
+      <c r="A16" s="22" t="s">
         <v>84</v>
       </c>
       <c r="B16" s="16">
@@ -3254,7 +3292,7 @@
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
-      <c r="N16" s="27">
+      <c r="N16" s="21">
         <v>10001</v>
       </c>
       <c r="O16" s="16"/>
@@ -3271,8 +3309,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="29" t="s">
+    <row r="17" spans="1:18">
+      <c r="A17" s="22" t="s">
         <v>87</v>
       </c>
       <c r="B17" s="16">
@@ -3303,7 +3341,7 @@
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="27">
+      <c r="N17" s="21">
         <v>10001</v>
       </c>
       <c r="O17" s="16"/>
@@ -3317,8 +3355,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="29" t="s">
+    <row r="18" spans="1:19">
+      <c r="A18" s="22" t="s">
         <v>89</v>
       </c>
       <c r="B18" s="16">
@@ -3349,7 +3387,7 @@
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
-      <c r="N18" s="27">
+      <c r="N18" s="21">
         <v>10001</v>
       </c>
       <c r="O18" s="16"/>
@@ -3366,8 +3404,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="29" t="s">
+    <row r="19" spans="1:18">
+      <c r="A19" s="22" t="s">
         <v>91</v>
       </c>
       <c r="B19" s="16">
@@ -3398,7 +3436,7 @@
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
-      <c r="N19" s="27">
+      <c r="N19" s="21">
         <v>10001</v>
       </c>
       <c r="O19" s="16"/>
@@ -3412,8 +3450,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="29" t="s">
+    <row r="20" spans="1:19">
+      <c r="A20" s="22" t="s">
         <v>93</v>
       </c>
       <c r="B20" s="16">
@@ -3444,7 +3482,7 @@
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
-      <c r="N20" s="27">
+      <c r="N20" s="21">
         <v>10001</v>
       </c>
       <c r="O20" s="16"/>
@@ -3461,8 +3499,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="29" t="s">
+    <row r="21" spans="1:18">
+      <c r="A21" s="22" t="s">
         <v>95</v>
       </c>
       <c r="B21" s="16">
@@ -3493,7 +3531,7 @@
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
-      <c r="N21" s="27">
+      <c r="N21" s="21">
         <v>10001</v>
       </c>
       <c r="O21" s="16"/>
@@ -3507,8 +3545,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="29" t="s">
+    <row r="22" spans="1:19">
+      <c r="A22" s="22" t="s">
         <v>97</v>
       </c>
       <c r="B22" s="16">
@@ -3539,7 +3577,7 @@
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
-      <c r="N22" s="27">
+      <c r="N22" s="21">
         <v>10001</v>
       </c>
       <c r="O22" s="16"/>
@@ -3557,7 +3595,7 @@
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="22" t="s">
         <v>99</v>
       </c>
       <c r="B23" s="16">
@@ -3588,7 +3626,7 @@
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
-      <c r="N23" s="27">
+      <c r="N23" s="21">
         <v>10001</v>
       </c>
       <c r="O23" s="16"/>
@@ -3608,45 +3646,45 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" s="12" customFormat="1" spans="1:20">
-      <c r="A24" s="26" t="s">
+    <row r="24" s="12" customFormat="1" spans="1:18">
+      <c r="A24" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="21">
         <v>20</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="27">
-        <v>0</v>
-      </c>
-      <c r="F24" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="27">
-        <v>0</v>
-      </c>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27">
-        <v>0</v>
-      </c>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O24" s="27">
+      <c r="D24" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="21">
+        <v>0</v>
+      </c>
+      <c r="F24" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21">
+        <v>0</v>
+      </c>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O24" s="21">
         <v>114</v>
       </c>
-      <c r="P24" s="27" t="b">
+      <c r="P24" s="21" t="b">
         <v>1</v>
       </c>
       <c r="Q24" s="16">
@@ -3656,8 +3694,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="29" t="s">
+    <row r="25" spans="1:18">
+      <c r="A25" s="22" t="s">
         <v>104</v>
       </c>
       <c r="B25" s="16">
@@ -3688,7 +3726,7 @@
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
-      <c r="N25" s="27">
+      <c r="N25" s="21">
         <v>10001</v>
       </c>
       <c r="O25" s="16"/>
@@ -3702,8 +3740,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="29" t="s">
+    <row r="26" spans="1:18">
+      <c r="A26" s="22" t="s">
         <v>106</v>
       </c>
       <c r="B26" s="16">
@@ -3734,7 +3772,7 @@
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
-      <c r="N26" s="27">
+      <c r="N26" s="21">
         <v>10001</v>
       </c>
       <c r="O26" s="16"/>
@@ -3748,8 +3786,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="29" t="s">
+    <row r="27" spans="1:18">
+      <c r="A27" s="22" t="s">
         <v>108</v>
       </c>
       <c r="B27" s="16">
@@ -3780,7 +3818,7 @@
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
-      <c r="N27" s="27">
+      <c r="N27" s="21">
         <v>10001</v>
       </c>
       <c r="O27" s="16"/>
@@ -3794,8 +3832,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="29" t="s">
+    <row r="28" spans="1:19">
+      <c r="A28" s="22" t="s">
         <v>110</v>
       </c>
       <c r="B28" s="16">
@@ -3826,7 +3864,7 @@
       </c>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
-      <c r="N28" s="27">
+      <c r="N28" s="21">
         <v>10001</v>
       </c>
       <c r="O28" s="16"/>
@@ -3843,8 +3881,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="29" t="s">
+    <row r="29" spans="1:18">
+      <c r="A29" s="22" t="s">
         <v>112</v>
       </c>
       <c r="B29" s="16">
@@ -3875,7 +3913,7 @@
       </c>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
-      <c r="N29" s="27">
+      <c r="N29" s="21">
         <v>10001</v>
       </c>
       <c r="O29" s="16"/>
@@ -3889,8 +3927,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="29" t="s">
+    <row r="30" spans="1:18">
+      <c r="A30" s="22" t="s">
         <v>114</v>
       </c>
       <c r="B30" s="16">
@@ -3921,7 +3959,7 @@
       </c>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
-      <c r="N30" s="27">
+      <c r="N30" s="21">
         <v>10001</v>
       </c>
       <c r="O30" s="16"/>
@@ -3935,8 +3973,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="29" t="s">
+    <row r="31" spans="1:18">
+      <c r="A31" s="22" t="s">
         <v>116</v>
       </c>
       <c r="B31" s="16">
@@ -3967,7 +4005,7 @@
       </c>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
-      <c r="N31" s="27">
+      <c r="N31" s="21">
         <v>10001</v>
       </c>
       <c r="O31" s="16"/>
@@ -3981,8 +4019,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" s="13" customFormat="1" spans="1:20">
-      <c r="A32" s="29" t="s">
+    <row r="32" s="13" customFormat="1" spans="1:18">
+      <c r="A32" s="22" t="s">
         <v>118</v>
       </c>
       <c r="B32" s="16">
@@ -4027,7 +4065,7 @@
       </c>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="22" t="s">
         <v>120</v>
       </c>
       <c r="B33" s="16">
@@ -4058,7 +4096,7 @@
       </c>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
-      <c r="N33" s="27">
+      <c r="N33" s="21">
         <v>10001</v>
       </c>
       <c r="O33" s="16"/>
@@ -4078,42 +4116,42 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" s="12" customFormat="1" spans="1:20">
-      <c r="A34" s="26" t="s">
+    <row r="34" s="12" customFormat="1" spans="1:19">
+      <c r="A34" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="21">
         <v>30</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="27">
-        <v>0</v>
-      </c>
-      <c r="F34" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" s="27">
-        <v>0</v>
-      </c>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27">
-        <v>0</v>
-      </c>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O34" s="27">
+      <c r="D34" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="21">
+        <v>0</v>
+      </c>
+      <c r="F34" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" s="21">
+        <v>0</v>
+      </c>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21">
+        <v>0</v>
+      </c>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O34" s="21">
         <v>115</v>
       </c>
       <c r="P34" s="16" t="b">
@@ -4129,8 +4167,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="29" t="s">
+    <row r="35" spans="1:18">
+      <c r="A35" s="22" t="s">
         <v>125</v>
       </c>
       <c r="B35" s="15">
@@ -4161,7 +4199,7 @@
       </c>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
-      <c r="N35" s="27">
+      <c r="N35" s="21">
         <v>10001</v>
       </c>
       <c r="P35" s="16" t="b">
@@ -4174,8 +4212,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="29" t="s">
+    <row r="36" spans="1:19">
+      <c r="A36" s="22" t="s">
         <v>127</v>
       </c>
       <c r="B36" s="15">
@@ -4206,7 +4244,7 @@
       </c>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
-      <c r="N36" s="27">
+      <c r="N36" s="21">
         <v>10001</v>
       </c>
       <c r="P36" s="16" t="b">
@@ -4222,8 +4260,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="29" t="s">
+    <row r="37" spans="1:18">
+      <c r="A37" s="22" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="15">
@@ -4254,7 +4292,7 @@
       </c>
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
-      <c r="N37" s="27">
+      <c r="N37" s="21">
         <v>10001</v>
       </c>
       <c r="P37" s="16" t="b">
@@ -4267,8 +4305,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
-      <c r="A38" s="29" t="s">
+    <row r="38" spans="1:19">
+      <c r="A38" s="22" t="s">
         <v>131</v>
       </c>
       <c r="B38" s="15">
@@ -4299,7 +4337,7 @@
       </c>
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
-      <c r="N38" s="27">
+      <c r="N38" s="21">
         <v>10001</v>
       </c>
       <c r="P38" s="16" t="b">
@@ -4316,7 +4354,7 @@
       </c>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="22" t="s">
         <v>133</v>
       </c>
       <c r="B39" s="15">
@@ -4347,7 +4385,7 @@
       </c>
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
-      <c r="N39" s="27">
+      <c r="N39" s="21">
         <v>10001</v>
       </c>
       <c r="P39" s="16" t="b">
@@ -4366,8 +4404,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
-      <c r="A40" s="29" t="s">
+    <row r="40" spans="1:19">
+      <c r="A40" s="22" t="s">
         <v>135</v>
       </c>
       <c r="B40" s="15">
@@ -4398,7 +4436,7 @@
       </c>
       <c r="L40" s="16"/>
       <c r="M40" s="16"/>
-      <c r="N40" s="27">
+      <c r="N40" s="21">
         <v>10001</v>
       </c>
       <c r="P40" s="16" t="b">
@@ -4414,8 +4452,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
-      <c r="A41" s="29" t="s">
+    <row r="41" spans="1:19">
+      <c r="A41" s="22" t="s">
         <v>137</v>
       </c>
       <c r="B41" s="15">
@@ -4446,7 +4484,7 @@
       </c>
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>
-      <c r="N41" s="27">
+      <c r="N41" s="21">
         <v>10001</v>
       </c>
       <c r="P41" s="16" t="b">
@@ -4462,8 +4500,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
-      <c r="A42" s="29" t="s">
+    <row r="42" spans="1:19">
+      <c r="A42" s="22" t="s">
         <v>139</v>
       </c>
       <c r="B42" s="15">
@@ -4494,7 +4532,7 @@
       </c>
       <c r="L42" s="16"/>
       <c r="M42" s="16"/>
-      <c r="N42" s="27">
+      <c r="N42" s="21">
         <v>10001</v>
       </c>
       <c r="P42" s="16" t="b">
@@ -4511,7 +4549,7 @@
       </c>
     </row>
     <row r="43" spans="1:20">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="22" t="s">
         <v>141</v>
       </c>
       <c r="B43" s="15">
@@ -4542,7 +4580,7 @@
       </c>
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
-      <c r="N43" s="27">
+      <c r="N43" s="21">
         <v>10001</v>
       </c>
       <c r="P43" s="16" t="b">
@@ -4561,42 +4599,42 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" s="12" customFormat="1" spans="1:20">
-      <c r="A44" s="26" t="s">
+    <row r="44" s="12" customFormat="1" spans="1:19">
+      <c r="A44" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="21">
         <v>40</v>
       </c>
-      <c r="C44" s="27" t="s">
+      <c r="C44" s="21" t="s">
         <v>144</v>
       </c>
       <c r="D44" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="21">
         <v>20</v>
       </c>
-      <c r="F44" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44" s="27">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27">
-        <v>0</v>
-      </c>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O44" s="27">
+      <c r="F44" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21">
+        <v>0</v>
+      </c>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21">
+        <v>0</v>
+      </c>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O44" s="21">
         <v>116</v>
       </c>
       <c r="P44" s="16" t="b">
@@ -4612,8 +4650,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
-      <c r="A45" s="29" t="s">
+    <row r="45" spans="1:19">
+      <c r="A45" s="22" t="s">
         <v>146</v>
       </c>
       <c r="B45" s="15">
@@ -4644,7 +4682,7 @@
       </c>
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
-      <c r="N45" s="27">
+      <c r="N45" s="21">
         <v>10001</v>
       </c>
       <c r="P45" s="16" t="b">
@@ -4660,8 +4698,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
-      <c r="A46" s="29" t="s">
+    <row r="46" spans="1:19">
+      <c r="A46" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B46" s="15">
@@ -4692,7 +4730,7 @@
       </c>
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
-      <c r="N46" s="27">
+      <c r="N46" s="21">
         <v>10001</v>
       </c>
       <c r="P46" s="16" t="b">
@@ -4708,8 +4746,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
-      <c r="A47" s="29" t="s">
+    <row r="47" spans="1:19">
+      <c r="A47" s="22" t="s">
         <v>150</v>
       </c>
       <c r="B47" s="15">
@@ -4740,7 +4778,7 @@
       </c>
       <c r="L47" s="16"/>
       <c r="M47" s="16"/>
-      <c r="N47" s="27">
+      <c r="N47" s="21">
         <v>10001</v>
       </c>
       <c r="P47" s="16" t="b">
@@ -4757,7 +4795,7 @@
       </c>
     </row>
     <row r="48" spans="1:20">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="22" t="s">
         <v>152</v>
       </c>
       <c r="B48" s="15">
@@ -4788,7 +4826,7 @@
       </c>
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
-      <c r="N48" s="27">
+      <c r="N48" s="21">
         <v>10001</v>
       </c>
       <c r="P48" s="16" t="b">
@@ -4807,8 +4845,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:20">
-      <c r="A49" s="29" t="s">
+    <row r="49" spans="1:19">
+      <c r="A49" s="22" t="s">
         <v>154</v>
       </c>
       <c r="B49" s="15">
@@ -4839,7 +4877,7 @@
       </c>
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
-      <c r="N49" s="27">
+      <c r="N49" s="21">
         <v>10001</v>
       </c>
       <c r="P49" s="16" t="b">
@@ -4855,8 +4893,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:20">
-      <c r="A50" s="29" t="s">
+    <row r="50" spans="1:19">
+      <c r="A50" s="22" t="s">
         <v>156</v>
       </c>
       <c r="B50" s="15">
@@ -4887,7 +4925,7 @@
       </c>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
-      <c r="N50" s="27">
+      <c r="N50" s="21">
         <v>10001</v>
       </c>
       <c r="P50" s="16" t="b">
@@ -4903,8 +4941,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:20">
-      <c r="A51" s="29" t="s">
+    <row r="51" spans="1:17">
+      <c r="A51" s="22" t="s">
         <v>158</v>
       </c>
       <c r="B51" s="15">
@@ -4935,7 +4973,7 @@
       </c>
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
-      <c r="N51" s="27">
+      <c r="N51" s="21">
         <v>10001</v>
       </c>
       <c r="P51" s="16" t="b">
@@ -4945,8 +4983,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:20">
-      <c r="A52" s="29" t="s">
+    <row r="52" spans="1:19">
+      <c r="A52" s="22" t="s">
         <v>160</v>
       </c>
       <c r="B52" s="15">
@@ -4977,7 +5015,7 @@
       </c>
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
-      <c r="N52" s="27">
+      <c r="N52" s="21">
         <v>10001</v>
       </c>
       <c r="P52" s="16" t="b">
@@ -4994,7 +5032,7 @@
       </c>
     </row>
     <row r="53" spans="1:20">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="22" t="s">
         <v>162</v>
       </c>
       <c r="B53" s="15">
@@ -5025,7 +5063,7 @@
       </c>
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>
-      <c r="N53" s="27">
+      <c r="N53" s="21">
         <v>10001</v>
       </c>
       <c r="P53" s="16" t="b">
@@ -5044,42 +5082,42 @@
         <v>145</v>
       </c>
     </row>
-    <row r="54" s="12" customFormat="1" spans="1:20">
-      <c r="A54" s="26" t="s">
+    <row r="54" s="12" customFormat="1" spans="1:19">
+      <c r="A54" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B54" s="27">
+      <c r="B54" s="21">
         <v>50</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="D54" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="27">
+      <c r="D54" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="21">
         <v>40</v>
       </c>
-      <c r="F54" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" s="27">
-        <v>0</v>
-      </c>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27">
-        <v>0</v>
-      </c>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O54" s="27">
+      <c r="F54" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="21">
+        <v>0</v>
+      </c>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21">
+        <v>0</v>
+      </c>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O54" s="21">
         <v>118</v>
       </c>
       <c r="P54" s="16" t="b">
@@ -5095,8 +5133,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="55" spans="1:20">
-      <c r="A55" s="29" t="s">
+    <row r="55" spans="1:19">
+      <c r="A55" s="22" t="s">
         <v>167</v>
       </c>
       <c r="B55" s="15">
@@ -5129,7 +5167,7 @@
       </c>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
-      <c r="N55" s="27">
+      <c r="N55" s="21">
         <v>10001</v>
       </c>
       <c r="O55" s="15">
@@ -5149,7 +5187,7 @@
       </c>
     </row>
     <row r="56" spans="1:20">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="22" t="s">
         <v>169</v>
       </c>
       <c r="B56" s="15">
@@ -5182,7 +5220,7 @@
       </c>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
-      <c r="N56" s="27">
+      <c r="N56" s="21">
         <v>10001</v>
       </c>
       <c r="P56" s="16" t="b">
@@ -5202,7 +5240,7 @@
       </c>
     </row>
     <row r="57" spans="1:20">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="22" t="s">
         <v>172</v>
       </c>
       <c r="B57" s="15">
@@ -5233,7 +5271,7 @@
       </c>
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
-      <c r="N57" s="27">
+      <c r="N57" s="21">
         <v>10001</v>
       </c>
       <c r="P57" s="16" t="b">
@@ -5252,8 +5290,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="58" s="11" customFormat="1" spans="1:20">
-      <c r="A58" s="29" t="s">
+    <row r="58" s="11" customFormat="1" spans="1:19">
+      <c r="A58" s="22" t="s">
         <v>174</v>
       </c>
       <c r="B58" s="16">
@@ -5282,7 +5320,7 @@
       </c>
       <c r="L58" s="16"/>
       <c r="M58" s="16"/>
-      <c r="N58" s="27">
+      <c r="N58" s="21">
         <v>10001</v>
       </c>
       <c r="P58" s="16" t="b">
@@ -5298,40 +5336,40 @@
         <v>145</v>
       </c>
     </row>
-    <row r="59" s="14" customFormat="1" spans="1:20">
-      <c r="A59" s="26" t="s">
+    <row r="59" s="14" customFormat="1" spans="1:19">
+      <c r="A59" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="21">
         <v>55</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="D59" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="27">
+      <c r="D59" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="21">
         <v>-155</v>
       </c>
       <c r="F59" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="G59" s="27">
+      <c r="G59" s="21">
         <v>60</v>
       </c>
-      <c r="I59" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" s="27">
-        <v>0</v>
-      </c>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O59" s="28"/>
+      <c r="I59" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" s="21">
+        <v>0</v>
+      </c>
+      <c r="L59" s="21"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O59" s="31"/>
       <c r="P59" s="16" t="b">
         <v>0</v>
       </c>
@@ -5346,42 +5384,42 @@
       </c>
     </row>
     <row r="60" s="14" customFormat="1" spans="1:20">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B60" s="27">
+      <c r="B60" s="21">
         <v>56</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="21" t="s">
         <v>180</v>
       </c>
       <c r="D60" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E60" s="27">
+      <c r="E60" s="21">
         <v>0</v>
       </c>
       <c r="F60" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="G60" s="27">
+      <c r="G60" s="21">
         <v>60</v>
       </c>
-      <c r="I60" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27">
-        <v>1</v>
-      </c>
-      <c r="K60" s="27">
-        <v>0</v>
-      </c>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O60" s="28"/>
+      <c r="I60" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" s="21">
+        <v>1</v>
+      </c>
+      <c r="K60" s="21">
+        <v>0</v>
+      </c>
+      <c r="L60" s="21"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O60" s="31"/>
       <c r="P60" s="16" t="b">
         <v>1</v>
       </c>
@@ -5398,8 +5436,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" s="11" customFormat="1" spans="1:20">
-      <c r="A61" s="29" t="s">
+    <row r="61" s="11" customFormat="1" spans="1:19">
+      <c r="A61" s="22" t="s">
         <v>182</v>
       </c>
       <c r="B61" s="16">
@@ -5429,7 +5467,7 @@
       </c>
       <c r="L61" s="16"/>
       <c r="M61" s="16"/>
-      <c r="N61" s="27">
+      <c r="N61" s="21">
         <v>10001</v>
       </c>
       <c r="P61" s="16" t="b">
@@ -5445,8 +5483,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="62" s="11" customFormat="1" spans="1:20">
-      <c r="A62" s="29" t="s">
+    <row r="62" s="11" customFormat="1" spans="1:19">
+      <c r="A62" s="22" t="s">
         <v>184</v>
       </c>
       <c r="B62" s="16">
@@ -5476,7 +5514,7 @@
       </c>
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
-      <c r="N62" s="27">
+      <c r="N62" s="21">
         <v>10001</v>
       </c>
       <c r="P62" s="16" t="b">
@@ -5492,8 +5530,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" s="11" customFormat="1" spans="1:20">
-      <c r="A63" s="29" t="s">
+    <row r="63" s="11" customFormat="1" spans="1:19">
+      <c r="A63" s="22" t="s">
         <v>186</v>
       </c>
       <c r="B63" s="16">
@@ -5523,7 +5561,7 @@
       </c>
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
-      <c r="N63" s="27">
+      <c r="N63" s="21">
         <v>10001</v>
       </c>
       <c r="P63" s="16" t="b">
@@ -5539,40 +5577,40 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" s="14" customFormat="1" spans="1:20">
-      <c r="A64" s="26" t="s">
+    <row r="64" s="14" customFormat="1" spans="1:19">
+      <c r="A64" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B64" s="27">
+      <c r="B64" s="21">
         <v>60</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C64" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="D64" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="27">
-        <v>0</v>
-      </c>
-      <c r="F64" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" s="27">
-        <v>0</v>
-      </c>
-      <c r="I64" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" s="27">
-        <v>0</v>
-      </c>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O64" s="27">
+      <c r="D64" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="21">
+        <v>0</v>
+      </c>
+      <c r="F64" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G64" s="21">
+        <v>0</v>
+      </c>
+      <c r="I64" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" s="21">
+        <v>0</v>
+      </c>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O64" s="21">
         <v>120</v>
       </c>
       <c r="P64" s="16" t="b">
@@ -5588,8 +5626,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="65" s="11" customFormat="1" spans="1:20">
-      <c r="A65" s="29" t="s">
+    <row r="65" s="11" customFormat="1" spans="1:19">
+      <c r="A65" s="22" t="s">
         <v>191</v>
       </c>
       <c r="B65" s="16">
@@ -5618,7 +5656,7 @@
       </c>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
-      <c r="N65" s="27">
+      <c r="N65" s="21">
         <v>10001</v>
       </c>
       <c r="P65" s="16" t="b">
@@ -5634,8 +5672,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" s="11" customFormat="1" spans="1:20">
-      <c r="A66" s="29" t="s">
+    <row r="66" s="11" customFormat="1" spans="1:18">
+      <c r="A66" s="22" t="s">
         <v>193</v>
       </c>
       <c r="B66" s="16">
@@ -5664,7 +5702,7 @@
       </c>
       <c r="L66" s="16"/>
       <c r="M66" s="16"/>
-      <c r="N66" s="27">
+      <c r="N66" s="21">
         <v>10001</v>
       </c>
       <c r="P66" s="16" t="b">
@@ -5677,8 +5715,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="67" s="11" customFormat="1" spans="1:20">
-      <c r="A67" s="29" t="s">
+    <row r="67" s="11" customFormat="1" spans="1:19">
+      <c r="A67" s="22" t="s">
         <v>195</v>
       </c>
       <c r="B67" s="16">
@@ -5707,7 +5745,7 @@
       </c>
       <c r="L67" s="16"/>
       <c r="M67" s="16"/>
-      <c r="N67" s="27">
+      <c r="N67" s="21">
         <v>10001</v>
       </c>
       <c r="P67" s="16" t="b">
@@ -5724,7 +5762,7 @@
       </c>
     </row>
     <row r="68" spans="1:20">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="22" t="s">
         <v>197</v>
       </c>
       <c r="B68" s="16">
@@ -5755,7 +5793,7 @@
       </c>
       <c r="L68" s="16"/>
       <c r="M68" s="16"/>
-      <c r="N68" s="27">
+      <c r="N68" s="21">
         <v>10001</v>
       </c>
       <c r="P68" s="16" t="b">
@@ -5775,7 +5813,7 @@
       </c>
     </row>
     <row r="69" spans="1:20">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="22" t="s">
         <v>199</v>
       </c>
       <c r="B69" s="16">
@@ -5806,7 +5844,7 @@
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
-      <c r="N69" s="27">
+      <c r="N69" s="21">
         <v>10001</v>
       </c>
       <c r="P69" s="16" t="b">
@@ -5826,7 +5864,7 @@
       </c>
     </row>
     <row r="70" spans="1:20">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="22" t="s">
         <v>201</v>
       </c>
       <c r="B70" s="16">
@@ -5857,7 +5895,7 @@
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="16"/>
-      <c r="N70" s="27">
+      <c r="N70" s="21">
         <v>10001</v>
       </c>
       <c r="P70" s="16" t="b">
@@ -5876,8 +5914,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="71" spans="1:20">
-      <c r="A71" s="29" t="s">
+    <row r="71" spans="1:17">
+      <c r="A71" s="22" t="s">
         <v>203</v>
       </c>
       <c r="B71" s="16">
@@ -5908,7 +5946,7 @@
       </c>
       <c r="L71" s="16"/>
       <c r="M71" s="16"/>
-      <c r="N71" s="27">
+      <c r="N71" s="21">
         <v>10001</v>
       </c>
       <c r="P71" s="16" t="b">
@@ -5919,7 +5957,7 @@
       </c>
     </row>
     <row r="72" spans="1:20">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="22" t="s">
         <v>205</v>
       </c>
       <c r="B72" s="16">
@@ -5950,7 +5988,7 @@
       </c>
       <c r="L72" s="16"/>
       <c r="M72" s="16"/>
-      <c r="N72" s="27">
+      <c r="N72" s="21">
         <v>10001</v>
       </c>
       <c r="P72" s="16" t="b">
@@ -5969,8 +6007,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:20">
-      <c r="A73" s="29" t="s">
+    <row r="73" spans="1:19">
+      <c r="A73" s="22" t="s">
         <v>207</v>
       </c>
       <c r="B73" s="16">
@@ -6001,7 +6039,7 @@
       </c>
       <c r="L73" s="16"/>
       <c r="M73" s="16"/>
-      <c r="N73" s="27">
+      <c r="N73" s="21">
         <v>10001</v>
       </c>
       <c r="P73" s="16" t="b">
@@ -6017,42 +6055,42 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" s="12" customFormat="1" spans="1:20">
-      <c r="A74" s="26" t="s">
+    <row r="74" s="12" customFormat="1" spans="1:19">
+      <c r="A74" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="B74" s="27">
+      <c r="B74" s="21">
         <v>70</v>
       </c>
-      <c r="C74" s="27" t="s">
+      <c r="C74" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="D74" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" s="27">
+      <c r="D74" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" s="21">
         <v>50</v>
       </c>
-      <c r="F74" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" s="27">
+      <c r="F74" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="21">
         <v>0</v>
       </c>
       <c r="H74" s="14"/>
-      <c r="I74" s="27" t="b">
+      <c r="I74" s="21" t="b">
         <v>0</v>
       </c>
       <c r="J74" s="14"/>
-      <c r="K74" s="27">
-        <v>0</v>
-      </c>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
-      <c r="N74" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O74" s="27">
+      <c r="K74" s="21">
+        <v>0</v>
+      </c>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O74" s="21">
         <v>121</v>
       </c>
       <c r="P74" s="16" t="b">
@@ -6068,8 +6106,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:20">
-      <c r="A75" s="29" t="s">
+    <row r="75" spans="1:19">
+      <c r="A75" s="22" t="s">
         <v>212</v>
       </c>
       <c r="B75" s="16">
@@ -6100,7 +6138,7 @@
       </c>
       <c r="L75" s="16"/>
       <c r="M75" s="16"/>
-      <c r="N75" s="27">
+      <c r="N75" s="21">
         <v>10001</v>
       </c>
       <c r="P75" s="16" t="b">
@@ -6116,8 +6154,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="76" spans="1:20">
-      <c r="A76" s="29" t="s">
+    <row r="76" spans="1:19">
+      <c r="A76" s="22" t="s">
         <v>214</v>
       </c>
       <c r="B76" s="16">
@@ -6148,7 +6186,7 @@
       </c>
       <c r="L76" s="16"/>
       <c r="M76" s="16"/>
-      <c r="N76" s="27">
+      <c r="N76" s="21">
         <v>10001</v>
       </c>
       <c r="P76" s="16" t="b">
@@ -6164,8 +6202,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="77" spans="1:20">
-      <c r="A77" s="29" t="s">
+    <row r="77" spans="1:18">
+      <c r="A77" s="22" t="s">
         <v>216</v>
       </c>
       <c r="B77" s="16">
@@ -6196,7 +6234,7 @@
       </c>
       <c r="L77" s="16"/>
       <c r="M77" s="16"/>
-      <c r="N77" s="27">
+      <c r="N77" s="21">
         <v>10001</v>
       </c>
       <c r="P77" s="16" t="b">
@@ -6209,8 +6247,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:20">
-      <c r="A78" s="29" t="s">
+    <row r="78" spans="1:19">
+      <c r="A78" s="22" t="s">
         <v>218</v>
       </c>
       <c r="B78" s="16">
@@ -6241,7 +6279,7 @@
       </c>
       <c r="L78" s="16"/>
       <c r="M78" s="16"/>
-      <c r="N78" s="27">
+      <c r="N78" s="21">
         <v>10001</v>
       </c>
       <c r="P78" s="16" t="b">
@@ -6258,7 +6296,7 @@
       </c>
     </row>
     <row r="79" spans="1:20">
-      <c r="A79" s="29" t="s">
+      <c r="A79" s="22" t="s">
         <v>220</v>
       </c>
       <c r="B79" s="16">
@@ -6289,7 +6327,7 @@
       </c>
       <c r="L79" s="16"/>
       <c r="M79" s="16"/>
-      <c r="N79" s="27">
+      <c r="N79" s="21">
         <v>10001</v>
       </c>
       <c r="P79" s="16" t="b">
@@ -6309,7 +6347,7 @@
       </c>
     </row>
     <row r="80" spans="1:20">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="22" t="s">
         <v>222</v>
       </c>
       <c r="B80" s="16">
@@ -6340,7 +6378,7 @@
       </c>
       <c r="L80" s="16"/>
       <c r="M80" s="16"/>
-      <c r="N80" s="27">
+      <c r="N80" s="21">
         <v>10001</v>
       </c>
       <c r="P80" s="16" t="b">
@@ -6359,8 +6397,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:20">
-      <c r="A81" s="29" t="s">
+    <row r="81" spans="1:19">
+      <c r="A81" s="22" t="s">
         <v>224</v>
       </c>
       <c r="B81" s="16">
@@ -6391,7 +6429,7 @@
       </c>
       <c r="L81" s="16"/>
       <c r="M81" s="16"/>
-      <c r="N81" s="27">
+      <c r="N81" s="21">
         <v>10001</v>
       </c>
       <c r="P81" s="16" t="b">
@@ -6407,8 +6445,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:20">
-      <c r="A82" s="29" t="s">
+    <row r="82" spans="1:19">
+      <c r="A82" s="22" t="s">
         <v>226</v>
       </c>
       <c r="B82" s="16">
@@ -6439,7 +6477,7 @@
       </c>
       <c r="L82" s="16"/>
       <c r="M82" s="16"/>
-      <c r="N82" s="27">
+      <c r="N82" s="21">
         <v>10001</v>
       </c>
       <c r="P82" s="16" t="b">
@@ -6455,8 +6493,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:20">
-      <c r="A83" s="29" t="s">
+    <row r="83" spans="1:19">
+      <c r="A83" s="22" t="s">
         <v>228</v>
       </c>
       <c r="B83" s="16">
@@ -6487,7 +6525,7 @@
       </c>
       <c r="L83" s="16"/>
       <c r="M83" s="16"/>
-      <c r="N83" s="27">
+      <c r="N83" s="21">
         <v>10001</v>
       </c>
       <c r="P83" s="16" t="b">
@@ -6503,8 +6541,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:20">
-      <c r="A84" s="29" t="s">
+    <row r="84" spans="1:18">
+      <c r="A84" s="22" t="s">
         <v>230</v>
       </c>
       <c r="B84" s="16">
@@ -6535,7 +6573,7 @@
       </c>
       <c r="L84" s="16"/>
       <c r="M84" s="16"/>
-      <c r="N84" s="27">
+      <c r="N84" s="21">
         <v>10001</v>
       </c>
       <c r="P84" s="16" t="b">
@@ -6549,7 +6587,7 @@
       </c>
     </row>
     <row r="85" spans="1:20">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="22" t="s">
         <v>232</v>
       </c>
       <c r="B85" s="16">
@@ -6580,7 +6618,7 @@
       </c>
       <c r="L85" s="16"/>
       <c r="M85" s="16"/>
-      <c r="N85" s="27">
+      <c r="N85" s="21">
         <v>10001</v>
       </c>
       <c r="P85" s="16" t="b">
@@ -6599,8 +6637,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="86" spans="1:20">
-      <c r="A86" s="29" t="s">
+    <row r="86" spans="1:19">
+      <c r="A86" s="22" t="s">
         <v>234</v>
       </c>
       <c r="B86" s="16">
@@ -6631,7 +6669,7 @@
       </c>
       <c r="L86" s="16"/>
       <c r="M86" s="16"/>
-      <c r="N86" s="27">
+      <c r="N86" s="21">
         <v>10001</v>
       </c>
       <c r="P86" s="16" t="b">
@@ -6647,8 +6685,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:20">
-      <c r="A87" s="29" t="s">
+    <row r="87" spans="1:18">
+      <c r="A87" s="22" t="s">
         <v>236</v>
       </c>
       <c r="B87" s="16">
@@ -6679,7 +6717,7 @@
       </c>
       <c r="L87" s="16"/>
       <c r="M87" s="16"/>
-      <c r="N87" s="27">
+      <c r="N87" s="21">
         <v>10001</v>
       </c>
       <c r="P87" s="16" t="b">
@@ -6693,7 +6731,7 @@
       </c>
     </row>
     <row r="88" spans="1:20">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="22" t="s">
         <v>238</v>
       </c>
       <c r="B88" s="16">
@@ -6724,7 +6762,7 @@
       </c>
       <c r="L88" s="16"/>
       <c r="M88" s="16"/>
-      <c r="N88" s="27">
+      <c r="N88" s="21">
         <v>10001</v>
       </c>
       <c r="P88" s="16" t="b">
@@ -6743,42 +6781,42 @@
         <v>211</v>
       </c>
     </row>
-    <row r="89" s="12" customFormat="1" spans="1:20">
-      <c r="A89" s="26" t="s">
+    <row r="89" s="12" customFormat="1" spans="1:19">
+      <c r="A89" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="B89" s="27">
+      <c r="B89" s="21">
         <v>85</v>
       </c>
-      <c r="C89" s="27" t="s">
+      <c r="C89" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="D89" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E89" s="27">
+      <c r="D89" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" s="21">
         <v>150</v>
       </c>
-      <c r="F89" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G89" s="27">
+      <c r="F89" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G89" s="21">
         <v>0</v>
       </c>
       <c r="H89" s="14"/>
-      <c r="I89" s="27" t="b">
+      <c r="I89" s="21" t="b">
         <v>0</v>
       </c>
       <c r="J89" s="14"/>
-      <c r="K89" s="27">
-        <v>0</v>
-      </c>
-      <c r="L89" s="27"/>
-      <c r="M89" s="27"/>
-      <c r="N89" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O89" s="27">
+      <c r="K89" s="21">
+        <v>0</v>
+      </c>
+      <c r="L89" s="21"/>
+      <c r="M89" s="21"/>
+      <c r="N89" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O89" s="21">
         <v>122</v>
       </c>
       <c r="P89" s="16" t="b">
@@ -6794,8 +6832,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="90" spans="1:20">
-      <c r="A90" s="29" t="s">
+    <row r="90" spans="1:19">
+      <c r="A90" s="22" t="s">
         <v>243</v>
       </c>
       <c r="B90" s="16">
@@ -6826,7 +6864,7 @@
       </c>
       <c r="L90" s="16"/>
       <c r="M90" s="16"/>
-      <c r="N90" s="27">
+      <c r="N90" s="21">
         <v>10001</v>
       </c>
       <c r="P90" s="16" t="b">
@@ -6842,8 +6880,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="91" spans="1:20">
-      <c r="A91" s="29" t="s">
+    <row r="91" spans="1:19">
+      <c r="A91" s="22" t="s">
         <v>245</v>
       </c>
       <c r="B91" s="16">
@@ -6874,7 +6912,7 @@
       </c>
       <c r="L91" s="16"/>
       <c r="M91" s="16"/>
-      <c r="N91" s="27">
+      <c r="N91" s="21">
         <v>10001</v>
       </c>
       <c r="P91" s="16" t="b">
@@ -6890,8 +6928,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="92" spans="1:20">
-      <c r="A92" s="29" t="s">
+    <row r="92" spans="1:18">
+      <c r="A92" s="22" t="s">
         <v>247</v>
       </c>
       <c r="B92" s="16">
@@ -6922,7 +6960,7 @@
       </c>
       <c r="L92" s="16"/>
       <c r="M92" s="16"/>
-      <c r="N92" s="27">
+      <c r="N92" s="21">
         <v>10001</v>
       </c>
       <c r="P92" s="16" t="b">
@@ -6936,7 +6974,7 @@
       </c>
     </row>
     <row r="93" spans="1:20">
-      <c r="A93" s="29" t="s">
+      <c r="A93" s="22" t="s">
         <v>249</v>
       </c>
       <c r="B93" s="16">
@@ -6967,7 +7005,7 @@
       </c>
       <c r="L93" s="16"/>
       <c r="M93" s="16"/>
-      <c r="N93" s="27">
+      <c r="N93" s="21">
         <v>10001</v>
       </c>
       <c r="P93" s="16" t="b">
@@ -6987,7 +7025,7 @@
       </c>
     </row>
     <row r="94" spans="1:20">
-      <c r="A94" s="29" t="s">
+      <c r="A94" s="22" t="s">
         <v>251</v>
       </c>
       <c r="B94" s="16">
@@ -7018,7 +7056,7 @@
       </c>
       <c r="L94" s="16"/>
       <c r="M94" s="16"/>
-      <c r="N94" s="27">
+      <c r="N94" s="21">
         <v>10001</v>
       </c>
       <c r="P94" s="16" t="b">
@@ -7037,8 +7075,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="95" spans="1:20">
-      <c r="A95" s="29" t="s">
+    <row r="95" spans="1:19">
+      <c r="A95" s="22" t="s">
         <v>253</v>
       </c>
       <c r="B95" s="16">
@@ -7069,7 +7107,7 @@
       </c>
       <c r="L95" s="16"/>
       <c r="M95" s="16"/>
-      <c r="N95" s="27">
+      <c r="N95" s="21">
         <v>10001</v>
       </c>
       <c r="P95" s="16" t="b">
@@ -7086,7 +7124,7 @@
       </c>
     </row>
     <row r="96" spans="1:20">
-      <c r="A96" s="29" t="s">
+      <c r="A96" s="22" t="s">
         <v>255</v>
       </c>
       <c r="B96" s="16">
@@ -7117,7 +7155,7 @@
       </c>
       <c r="L96" s="16"/>
       <c r="M96" s="16"/>
-      <c r="N96" s="27">
+      <c r="N96" s="21">
         <v>10001</v>
       </c>
       <c r="P96" s="16" t="b">
@@ -7136,8 +7174,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="97" spans="1:20">
-      <c r="A97" s="29" t="s">
+    <row r="97" spans="1:18">
+      <c r="A97" s="22" t="s">
         <v>257</v>
       </c>
       <c r="B97" s="16">
@@ -7168,7 +7206,7 @@
       </c>
       <c r="L97" s="16"/>
       <c r="M97" s="16"/>
-      <c r="N97" s="27">
+      <c r="N97" s="21">
         <v>10001</v>
       </c>
       <c r="P97" s="16" t="b">
@@ -7182,7 +7220,7 @@
       </c>
     </row>
     <row r="98" spans="1:20">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="22" t="s">
         <v>259</v>
       </c>
       <c r="B98" s="16">
@@ -7213,7 +7251,7 @@
       </c>
       <c r="L98" s="16"/>
       <c r="M98" s="16"/>
-      <c r="N98" s="27">
+      <c r="N98" s="21">
         <v>10001</v>
       </c>
       <c r="P98" s="16" t="b">
@@ -7233,7 +7271,7 @@
       </c>
     </row>
     <row r="99" spans="1:20">
-      <c r="A99" s="29" t="s">
+      <c r="A99" s="22" t="s">
         <v>261</v>
       </c>
       <c r="B99" s="16">
@@ -7264,7 +7302,7 @@
       </c>
       <c r="L99" s="16"/>
       <c r="M99" s="16"/>
-      <c r="N99" s="27">
+      <c r="N99" s="21">
         <v>10001</v>
       </c>
       <c r="P99" s="16" t="b">
@@ -7284,7 +7322,7 @@
       </c>
     </row>
     <row r="100" spans="1:20">
-      <c r="A100" s="29" t="s">
+      <c r="A100" s="22" t="s">
         <v>263</v>
       </c>
       <c r="B100" s="16">
@@ -7315,7 +7353,7 @@
       </c>
       <c r="L100" s="16"/>
       <c r="M100" s="16"/>
-      <c r="N100" s="27">
+      <c r="N100" s="21">
         <v>10001</v>
       </c>
       <c r="P100" s="16" t="b">
@@ -7334,8 +7372,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:20">
-      <c r="A101" s="29" t="s">
+    <row r="101" spans="1:19">
+      <c r="A101" s="22" t="s">
         <v>265</v>
       </c>
       <c r="B101" s="16">
@@ -7366,7 +7404,7 @@
       </c>
       <c r="L101" s="16"/>
       <c r="M101" s="16"/>
-      <c r="N101" s="27">
+      <c r="N101" s="21">
         <v>10001</v>
       </c>
       <c r="P101" s="16" t="b">
@@ -7383,7 +7421,7 @@
       </c>
     </row>
     <row r="102" spans="1:20">
-      <c r="A102" s="29" t="s">
+      <c r="A102" s="22" t="s">
         <v>267</v>
       </c>
       <c r="B102" s="16">
@@ -7414,7 +7452,7 @@
       </c>
       <c r="L102" s="16"/>
       <c r="M102" s="16"/>
-      <c r="N102" s="27">
+      <c r="N102" s="21">
         <v>10001</v>
       </c>
       <c r="P102" s="16" t="b">
@@ -7434,7 +7472,7 @@
       </c>
     </row>
     <row r="103" spans="1:20">
-      <c r="A103" s="29" t="s">
+      <c r="A103" s="22" t="s">
         <v>269</v>
       </c>
       <c r="B103" s="16">
@@ -7465,7 +7503,7 @@
       </c>
       <c r="L103" s="16"/>
       <c r="M103" s="16"/>
-      <c r="N103" s="27">
+      <c r="N103" s="21">
         <v>10001</v>
       </c>
       <c r="P103" s="16" t="b">
@@ -7484,42 +7522,42 @@
         <v>242</v>
       </c>
     </row>
-    <row r="104" s="12" customFormat="1" spans="1:20">
-      <c r="A104" s="26" t="s">
+    <row r="104" s="12" customFormat="1" spans="1:19">
+      <c r="A104" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="B104" s="27">
+      <c r="B104" s="21">
         <v>100</v>
       </c>
-      <c r="C104" s="27" t="s">
+      <c r="C104" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="D104" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E104" s="27">
+      <c r="D104" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" s="21">
         <v>140</v>
       </c>
-      <c r="F104" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G104" s="27">
+      <c r="F104" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G104" s="21">
         <v>0</v>
       </c>
       <c r="H104" s="14"/>
-      <c r="I104" s="27" t="b">
+      <c r="I104" s="21" t="b">
         <v>0</v>
       </c>
       <c r="J104" s="14"/>
-      <c r="K104" s="27">
-        <v>0</v>
-      </c>
-      <c r="L104" s="27"/>
-      <c r="M104" s="27"/>
-      <c r="N104" s="27">
-        <v>10001</v>
-      </c>
-      <c r="O104" s="27">
+      <c r="K104" s="21">
+        <v>0</v>
+      </c>
+      <c r="L104" s="21"/>
+      <c r="M104" s="21"/>
+      <c r="N104" s="21">
+        <v>10001</v>
+      </c>
+      <c r="O104" s="21">
         <v>123</v>
       </c>
       <c r="P104" s="16" t="b">
@@ -7535,8 +7573,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="105" spans="1:20">
-      <c r="A105" s="29" t="s">
+    <row r="105" spans="1:19">
+      <c r="A105" s="22" t="s">
         <v>274</v>
       </c>
       <c r="B105" s="16">
@@ -7567,7 +7605,7 @@
       </c>
       <c r="L105" s="16"/>
       <c r="M105" s="16"/>
-      <c r="N105" s="27">
+      <c r="N105" s="21">
         <v>10001</v>
       </c>
       <c r="P105" s="16" t="b">
@@ -7583,8 +7621,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="106" spans="1:20">
-      <c r="A106" s="29" t="s">
+    <row r="106" spans="1:18">
+      <c r="A106" s="22" t="s">
         <v>276</v>
       </c>
       <c r="B106" s="16">
@@ -7615,7 +7653,7 @@
       </c>
       <c r="L106" s="16"/>
       <c r="M106" s="16"/>
-      <c r="N106" s="27">
+      <c r="N106" s="21">
         <v>10001</v>
       </c>
       <c r="P106" s="16" t="b">
@@ -7628,8 +7666,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="107" spans="1:20">
-      <c r="A107" s="29" t="s">
+    <row r="107" spans="1:18">
+      <c r="A107" s="22" t="s">
         <v>278</v>
       </c>
       <c r="B107" s="16">
@@ -7660,7 +7698,7 @@
       </c>
       <c r="L107" s="16"/>
       <c r="M107" s="16"/>
-      <c r="N107" s="27">
+      <c r="N107" s="21">
         <v>10001</v>
       </c>
       <c r="P107" s="16" t="b">
@@ -7673,8 +7711,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="108" spans="1:20">
-      <c r="A108" s="29" t="s">
+    <row r="108" spans="1:19">
+      <c r="A108" s="22" t="s">
         <v>280</v>
       </c>
       <c r="B108" s="16">
@@ -7705,7 +7743,7 @@
       </c>
       <c r="L108" s="16"/>
       <c r="M108" s="16"/>
-      <c r="N108" s="27">
+      <c r="N108" s="21">
         <v>10001</v>
       </c>
       <c r="P108" s="16" t="b">
@@ -7722,7 +7760,7 @@
       </c>
     </row>
     <row r="109" spans="1:20">
-      <c r="A109" s="29" t="s">
+      <c r="A109" s="22" t="s">
         <v>282</v>
       </c>
       <c r="B109" s="16">
@@ -7753,7 +7791,7 @@
       </c>
       <c r="L109" s="16"/>
       <c r="M109" s="16"/>
-      <c r="N109" s="27">
+      <c r="N109" s="21">
         <v>10001</v>
       </c>
       <c r="P109" s="16" t="b">
@@ -7773,7 +7811,7 @@
       </c>
     </row>
     <row r="110" spans="1:20">
-      <c r="A110" s="29" t="s">
+      <c r="A110" s="22" t="s">
         <v>284</v>
       </c>
       <c r="B110" s="16">
@@ -7804,7 +7842,7 @@
       </c>
       <c r="L110" s="16"/>
       <c r="M110" s="16"/>
-      <c r="N110" s="27">
+      <c r="N110" s="21">
         <v>10001</v>
       </c>
       <c r="P110" s="16" t="b">
@@ -7823,8 +7861,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="111" spans="1:20">
-      <c r="A111" s="29" t="s">
+    <row r="111" spans="1:18">
+      <c r="A111" s="22" t="s">
         <v>286</v>
       </c>
       <c r="B111" s="16">
@@ -7855,7 +7893,7 @@
       </c>
       <c r="L111" s="16"/>
       <c r="M111" s="16"/>
-      <c r="N111" s="27">
+      <c r="N111" s="21">
         <v>10001</v>
       </c>
       <c r="P111" s="16" t="b">
@@ -7869,7 +7907,7 @@
       </c>
     </row>
     <row r="112" spans="1:20">
-      <c r="A112" s="29" t="s">
+      <c r="A112" s="22" t="s">
         <v>288</v>
       </c>
       <c r="B112" s="16">
@@ -7900,7 +7938,7 @@
       </c>
       <c r="L112" s="16"/>
       <c r="M112" s="16"/>
-      <c r="N112" s="27">
+      <c r="N112" s="21">
         <v>10001</v>
       </c>
       <c r="P112" s="16" t="b">
@@ -7920,7 +7958,7 @@
       </c>
     </row>
     <row r="113" spans="1:20">
-      <c r="A113" s="29" t="s">
+      <c r="A113" s="22" t="s">
         <v>290</v>
       </c>
       <c r="B113" s="16">
@@ -7951,7 +7989,7 @@
       </c>
       <c r="L113" s="16"/>
       <c r="M113" s="16"/>
-      <c r="N113" s="27">
+      <c r="N113" s="21">
         <v>10001</v>
       </c>
       <c r="P113" s="16" t="b">
@@ -7971,7 +8009,7 @@
       </c>
     </row>
     <row r="114" spans="1:20">
-      <c r="A114" s="29" t="s">
+      <c r="A114" s="22" t="s">
         <v>292</v>
       </c>
       <c r="B114" s="16">
@@ -8002,7 +8040,7 @@
       </c>
       <c r="L114" s="16"/>
       <c r="M114" s="16"/>
-      <c r="N114" s="27">
+      <c r="N114" s="21">
         <v>10001</v>
       </c>
       <c r="P114" s="16" t="b">
@@ -8021,8 +8059,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:20">
-      <c r="A115" s="29" t="s">
+    <row r="115" spans="1:18">
+      <c r="A115" s="22" t="s">
         <v>294</v>
       </c>
       <c r="B115" s="16">
@@ -8053,7 +8091,7 @@
       </c>
       <c r="L115" s="16"/>
       <c r="M115" s="16"/>
-      <c r="N115" s="27">
+      <c r="N115" s="21">
         <v>10001</v>
       </c>
       <c r="P115" s="16" t="b">
@@ -8067,7 +8105,7 @@
       </c>
     </row>
     <row r="116" spans="1:20">
-      <c r="A116" s="29" t="s">
+      <c r="A116" s="22" t="s">
         <v>296</v>
       </c>
       <c r="B116" s="16">
@@ -8098,7 +8136,7 @@
       </c>
       <c r="L116" s="16"/>
       <c r="M116" s="16"/>
-      <c r="N116" s="27">
+      <c r="N116" s="21">
         <v>10001</v>
       </c>
       <c r="P116" s="16" t="b">
@@ -8118,7 +8156,7 @@
       </c>
     </row>
     <row r="117" spans="1:20">
-      <c r="A117" s="29" t="s">
+      <c r="A117" s="22" t="s">
         <v>298</v>
       </c>
       <c r="B117" s="16">
@@ -8149,7 +8187,7 @@
       </c>
       <c r="L117" s="16"/>
       <c r="M117" s="16"/>
-      <c r="N117" s="27">
+      <c r="N117" s="21">
         <v>10001</v>
       </c>
       <c r="P117" s="16" t="b">
@@ -8169,7 +8207,7 @@
       </c>
     </row>
     <row r="118" spans="1:20">
-      <c r="A118" s="29" t="s">
+      <c r="A118" s="22" t="s">
         <v>300</v>
       </c>
       <c r="B118" s="16">
@@ -8199,7 +8237,7 @@
       </c>
       <c r="L118" s="16"/>
       <c r="M118" s="16"/>
-      <c r="N118" s="27">
+      <c r="N118" s="21">
         <v>10001</v>
       </c>
       <c r="P118" s="16" t="b">
@@ -8218,8 +8256,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="119" spans="1:20">
-      <c r="A119" s="29" t="s">
+    <row r="119" spans="1:18">
+      <c r="A119" s="22" t="s">
         <v>302</v>
       </c>
       <c r="B119" s="16">
@@ -8250,7 +8288,7 @@
       </c>
       <c r="L119" s="16"/>
       <c r="M119" s="16"/>
-      <c r="N119" s="27">
+      <c r="N119" s="21">
         <v>10001</v>
       </c>
       <c r="P119" s="16" t="b">
@@ -8264,7 +8302,7 @@
       </c>
     </row>
     <row r="120" spans="1:20">
-      <c r="A120" s="29" t="s">
+      <c r="A120" s="22" t="s">
         <v>304</v>
       </c>
       <c r="B120" s="16">
@@ -8295,7 +8333,7 @@
       </c>
       <c r="L120" s="16"/>
       <c r="M120" s="16"/>
-      <c r="N120" s="27">
+      <c r="N120" s="21">
         <v>10001</v>
       </c>
       <c r="P120" s="16" t="b">
@@ -8314,8 +8352,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="1:20">
-      <c r="A121" s="29" t="s">
+    <row r="121" spans="1:19">
+      <c r="A121" s="22" t="s">
         <v>306</v>
       </c>
       <c r="B121" s="16">
@@ -8345,7 +8383,7 @@
       <c r="K121" s="15">
         <v>0</v>
       </c>
-      <c r="N121" s="27">
+      <c r="N121" s="21">
         <v>10001</v>
       </c>
       <c r="P121" s="16" t="b">
@@ -8362,7 +8400,7 @@
       </c>
     </row>
     <row r="122" spans="1:20">
-      <c r="A122" s="29" t="s">
+      <c r="A122" s="22" t="s">
         <v>308</v>
       </c>
       <c r="B122" s="16">
@@ -8392,7 +8430,7 @@
       </c>
       <c r="L122" s="16"/>
       <c r="M122" s="16"/>
-      <c r="N122" s="27">
+      <c r="N122" s="21">
         <v>10001</v>
       </c>
       <c r="P122" s="16" t="b">
@@ -8411,8 +8449,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:20">
-      <c r="A123" s="29" t="s">
+    <row r="123" spans="1:19">
+      <c r="A123" s="22" t="s">
         <v>310</v>
       </c>
       <c r="B123" s="16">
@@ -8442,7 +8480,7 @@
       </c>
       <c r="L123" s="16"/>
       <c r="M123" s="16"/>
-      <c r="N123" s="27">
+      <c r="N123" s="21">
         <v>10001</v>
       </c>
       <c r="P123" s="16" t="b">
@@ -8459,6 +8497,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:T123" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
@@ -8473,12 +8512,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="14.2477876106195" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.6283185840708" style="8" customWidth="1"/>
-    <col min="3" max="3" width="12.2477876106195" style="8" customWidth="1"/>
-    <col min="4" max="4" width="11.1238938053097" style="8" customWidth="1"/>
+    <col min="1" max="1" width="14.25" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="8" customWidth="1"/>
     <col min="5" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
@@ -8524,7 +8563,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="2:4">
       <c r="B4" s="8">
         <v>1</v>
       </c>
@@ -8535,7 +8574,7 @@
         <v>20001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="2:4">
       <c r="B5" s="8">
         <v>2</v>
       </c>
@@ -8546,7 +8585,7 @@
         <v>20002</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="2:4">
       <c r="B6" s="8">
         <v>3</v>
       </c>
@@ -8557,7 +8596,7 @@
         <v>20003</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="2:4">
       <c r="B7" s="8">
         <v>4</v>
       </c>
@@ -8568,7 +8607,7 @@
         <v>20004</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="2:4">
       <c r="B8" s="8">
         <v>5</v>
       </c>
@@ -8579,7 +8618,7 @@
         <v>20005</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="2:4">
       <c r="B9" s="11">
         <v>6</v>
       </c>
@@ -8590,7 +8629,7 @@
         <v>20006</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="2:4">
       <c r="B10" s="8">
         <v>7</v>
       </c>
@@ -8601,7 +8640,7 @@
         <v>20007</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="2:4">
       <c r="B11" s="8">
         <v>8</v>
       </c>
@@ -8612,7 +8651,7 @@
         <v>20008</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="2:4">
       <c r="B12" s="8">
         <v>9</v>
       </c>
@@ -8623,7 +8662,7 @@
         <v>20009</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="2:4">
       <c r="B13" s="8">
         <v>10</v>
       </c>
@@ -8634,7 +8673,7 @@
         <v>20010</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="2:4">
       <c r="B14" s="8">
         <v>11</v>
       </c>
@@ -8645,7 +8684,7 @@
         <v>20011</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="2:4">
       <c r="B15" s="8">
         <v>12</v>
       </c>
@@ -8656,7 +8695,7 @@
         <v>20012</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="2:4">
       <c r="B16" s="8">
         <v>13</v>
       </c>
@@ -8811,6 +8850,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -8820,15 +8860,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.6283185840708" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.3716814159292" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="24" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.8761061946903" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.7522123893805" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.75" style="2" customWidth="1"/>
     <col min="6" max="6" width="25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.2477876106195" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.25" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -8851,7 +8891,7 @@
       <c r="F1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
@@ -8869,12 +8909,12 @@
       <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -8894,7 +8934,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>67</v>
       </c>
@@ -8910,11 +8950,11 @@
       <c r="E4" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>80</v>
       </c>
@@ -8930,51 +8970,51 @@
       <c r="E5" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>337</v>
       </c>
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>103</v>
       </c>
@@ -8990,51 +9030,51 @@
       <c r="E8" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>342</v>
       </c>
       <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>124</v>
       </c>
@@ -9050,11 +9090,11 @@
       <c r="E11" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>145</v>
       </c>
@@ -9070,11 +9110,11 @@
       <c r="E12" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>166</v>
       </c>
@@ -9090,11 +9130,11 @@
       <c r="E13" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>178</v>
       </c>
@@ -9110,11 +9150,11 @@
       <c r="E14" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>190</v>
       </c>
@@ -9130,11 +9170,11 @@
       <c r="E15" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>211</v>
       </c>
@@ -9150,7 +9190,7 @@
       <c r="E16" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>331</v>
       </c>
     </row>
@@ -9170,7 +9210,7 @@
       <c r="E17" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>331</v>
       </c>
     </row>
@@ -9190,17 +9230,166 @@
       <c r="E18" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="F20" s="5"/>
+    <row r="20" spans="6:6">
+      <c r="F20" s="6"/>
     </row>
   </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <commentList sheetStid="1">
+    <commentChains s:ref="K3" rgbClr="FF0000">
+      <unresolved>
+        <commentChain chainId="0270915ecd98d2577fa7f7ef5d9a4b8806a01eb1">
+          <item id="eaa1eff3dcd6438fa99215a72f401cbe20374b60" isNormal="1">
+            <s:text>
+              <s:r>
+                <s:t xml:space="preserve">Like：
+0-普通
+1-困难
+2-超级困难
+</s:t>
+              </s:r>
+            </s:text>
+          </item>
+        </commentChain>
+      </unresolved>
+      <resolved/>
+    </commentChains>
+    <commentChains s:ref="N3" rgbClr="FF0000">
+      <unresolved>
+        <commentChain chainId="6e02205e9276c07c92407cd7684a8d914a7076f7">
+          <item id="9952d9e6ade5b80c9867a38f25e66457fb0e006e" isNormal="1">
+            <s:text>
+              <s:r>
+                <s:t xml:space="preserve">LIKE:
+奖励分为：货币和道具
+注意：一些道具或者货币的奖励下发区分发送个数还是增加无限时间
+货币奖励：
+0体力
+1-金币
+2-生命
+道具奖励：
+1-撤回；
+2-打乱；
+3-销毁一组；
+4-移出；
+5-提示；
+6-拉霸；
+7-加槽</s:t>
+              </s:r>
+            </s:text>
+          </item>
+        </commentChain>
+      </unresolved>
+      <resolved/>
+    </commentChains>
+    <commentChains s:ref="Q3" rgbClr="FF0000">
+      <unresolved>
+        <commentChain chainId="7865d927b925d9b8614385af085f69be7e2b7f92">
+          <item id="0a9e003ad12df08c5504df2f47881015529080ea" isNormal="1">
+            <s:text>
+              <s:r>
+                <s:t xml:space="preserve">LIKE：
+0-不进入循环关卡（比如带有引导的）
+1-能进入循环关卡，（可带有金块的）
+2-能进入循环关卡，（不可带有金块）</s:t>
+              </s:r>
+            </s:text>
+          </item>
+        </commentChain>
+      </unresolved>
+      <resolved/>
+    </commentChains>
+  </commentList>
+  <commentList sheetStid="3">
+    <commentChains s:ref="C3" rgbClr="FF0000">
+      <unresolved>
+        <commentChain chainId="ff6b732ad142fc8ec94843520e3defcd71dc0f58">
+          <item id="f50174ad23612721563a2740b951b4f225e8d88a" isNormal="1">
+            <s:text>
+              <s:r>
+                <s:t xml:space="preserve">LIKE：
+进度类型分为两种：
+特殊棋子；
+游戏活动。
+</s:t>
+              </s:r>
+            </s:text>
+          </item>
+        </commentChain>
+      </unresolved>
+      <resolved/>
+    </commentChains>
+  </commentList>
+</comments>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <woSheetsProps>
+    <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="2" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+    <woSheetProps sheetStid="3" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
+      <cellprotection/>
+      <appEtDbRelations/>
+    </woSheetProps>
+  </woSheetsProps>
+  <woBookProps>
+    <bookSettings fileId="" isFilterShared="1" coreConquerUserId="" isAutoUpdatePaused="0" filterType="conn" isMergeTasksAutoUpdate="0" isInserPicAsAttachment="0"/>
+  </woBookProps>
+</woProps>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+  <pixelatorList sheetStid="4"/>
+</pixelators>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>